--- a/backend/rent.xlsx
+++ b/backend/rent.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -465,7 +465,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>ยืมอยู่</v>
+        <v>เกินกำหนด</v>
       </c>
     </row>
     <row r="4">
@@ -488,7 +488,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>ยืมอยู่</v>
+        <v>เกินกำหนด</v>
       </c>
     </row>
     <row r="5">
@@ -511,12 +511,35 @@
         <v/>
       </c>
       <c r="G5" t="str">
+        <v>เกินกำหนด</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>800060085845</v>
+      </c>
+      <c r="B6" t="str">
+        <v>นางสาว กนกวลี โพธิ์ศรี</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ศูนย์หนั้ตั้งยึด</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
         <v>ยืมอยู่</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/rent.xlsx
+++ b/backend/rent.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -534,12 +534,58 @@
         <v/>
       </c>
       <c r="G6" t="str">
+        <v>เกินกำหนด</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>863094651081</v>
+      </c>
+      <c r="B7" t="str">
+        <v>นาย ณัฐกิจ พากรกิจ</v>
+      </c>
+      <c r="C7" t="str">
+        <v>ศูนย์หนี้</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>ยืมอยู่</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>800094988865</v>
+      </c>
+      <c r="B8" t="str">
+        <v>นาย สมัย ยั่งยืน</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ศูนย์หนี้</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
         <v>ยืมอยู่</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
   </ignoredErrors>
 </worksheet>
 </file>